--- a/output/full_scan/batch_seq1_2026-10-29.xlsx
+++ b/output/full_scan/batch_seq1_2026-10-29.xlsx
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>745.0539977675729</v>
+        <v>935.0539977675729</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>13.8</v>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>73.04942590625882</v>
+        <v>73.04942620592021</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>48.0941620170606</v>
+        <v>48.09416227050815</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>1.605399776757287</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.06411553231799734</v>
+        <v>0.06411553226192916</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>1216</v>
+        <v>1101</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>684.1560659893451</v>
+        <v>875.2040972636464</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>79</v>
+        <v>28.2</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,49 +605,49 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>59.96082679167294</v>
+        <v>68.07539706846589</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>30.15163195935946</v>
+        <v>53.84259327382599</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.5156065989345001</v>
+        <v>0.6274758164665414</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2384061609837745</v>
+        <v>0.1380009886206763</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>1315</v>
+        <v>1439</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>達新</t>
+          <t>雋揚</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>682.5298255987899</v>
+        <v>823.6910361258283</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>72.5</v>
+        <v>29.4</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>57.46309256049918</v>
+        <v>52.79264988633372</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>51.26653022715605</v>
+        <v>12.70945923697407</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.321115603158335</v>
+        <v>2.969948518695487</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>-0.1422068443009472</v>
+        <v>0.3472540428199324</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, breakout_20d, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>1102</v>
+        <v>1303</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>677.1179395207143</v>
+        <v>816.5309668339227</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>37.8</v>
+        <v>312</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,49 +711,49 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>62.10143830022469</v>
+        <v>58.31853232603972</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>35.21679399483698</v>
+        <v>39.75180282442614</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.7032699209829498</v>
+        <v>0.7101657592705942</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.03710954606742156</v>
+        <v>-2.389913397204904</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, liquidity_ok, adx_trending, stronger_than_market, invest_trust_buy_2d, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>1439</v>
+        <v>1216</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>雋揚</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>658.6910361258283</v>
+        <v>814.1560659893451</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>29.4</v>
+        <v>79</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>52.79264987853185</v>
+        <v>59.96082685752868</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>12.70945923697407</v>
+        <v>30.15163205415603</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>2.969948518695487</v>
+        <v>0.5156065989345001</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.3472540429040328</v>
+        <v>0.2384061609837745</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>1201</v>
+        <v>1569</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>味全</t>
+          <t>濱川</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>655.9040071750061</v>
+        <v>768.5195049111977</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>12.35</v>
+        <v>92.3</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>69.80360662753704</v>
+        <v>70.65941377112966</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>38.53138564218026</v>
+        <v>68.26401597303028</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>4.276222621869944</v>
+        <v>1.710169730682238</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.08602270446395453</v>
+        <v>1.219679954492529</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>1101</v>
+        <v>1321</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>台泥</t>
+          <t>大洋</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>650.2040972636464</v>
+        <v>766.8609791727314</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>28.2</v>
+        <v>35.35</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>68.07539715603319</v>
+        <v>66.76815739341285</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>53.84259330627665</v>
+        <v>33.06846205078433</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.6274758164665414</v>
+        <v>0.4881242600126688</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1380009886206763</v>
+        <v>0.09672958880828075</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>1416</v>
+        <v>1201</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>廣豐</t>
+          <t>味全</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>649.0614708042974</v>
+        <v>765.9040071750061</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>13.3</v>
+        <v>12.35</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>71.88781710488139</v>
+        <v>69.80360668331615</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>47.89604768617018</v>
+        <v>38.53138575800241</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.9459730856750583</v>
+        <v>4.276222621869944</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.05320251890611466</v>
+        <v>0.08602270444993661</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>1569</v>
+        <v>1315</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>濱川</t>
+          <t>達新</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>628.5195049111977</v>
+        <v>762.5298255987899</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>92.3</v>
+        <v>72.5</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>70.65941373894427</v>
+        <v>57.46309249917511</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>68.26401604972872</v>
+        <v>51.26653022783758</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.710169730682238</v>
+        <v>0.321115603158335</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>1.219679954072028</v>
+        <v>-0.142206844104696</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>1528</v>
+        <v>1236</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>恩德</t>
+          <t>宏亞</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>618.6838474256461</v>
+        <v>751.1478862895517</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>25.8</v>
+        <v>26.45</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>57.83685645456401</v>
+        <v>65.02547097372644</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>30.49737274214619</v>
+        <v>23.81799622166764</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.184779576862051</v>
+        <v>0.7122080211546937</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.05477522215617192</v>
+        <v>0.0771242180761168</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>1326</v>
+        <v>1416</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>台化</t>
+          <t>廣豐</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>606.3386574964164</v>
+        <v>719.0614708042974</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>74.40000000000001</v>
+        <v>13.3</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>52.08924709402395</v>
+        <v>71.88781714212993</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>31.56302753462264</v>
+        <v>47.89604768617018</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.3071732137341162</v>
+        <v>0.9459730856750583</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-0.5843604075717845</v>
+        <v>0.05320251889209737</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>1321</v>
+        <v>1528</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>大洋</t>
+          <t>恩德</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>601.8609791727315</v>
+        <v>718.6838474256461</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>35.35</v>
+        <v>25.8</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>66.7681571940301</v>
+        <v>57.83685648712053</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>33.06846211583773</v>
+        <v>30.49737278204125</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.4881242600126688</v>
+        <v>1.184779576862051</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.09672958899050932</v>
+        <v>0.05477522211412034</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>1312</v>
+        <v>1102</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>國喬</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>601.7370516241933</v>
+        <v>692.1179395207143</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>14.35</v>
+        <v>37.8</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>44.16603869255671</v>
+        <v>62.10143827281055</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>34.63017363764819</v>
+        <v>35.21679398286587</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.2206517074519842</v>
+        <v>0.7032699209829498</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-0.2659972571497295</v>
+        <v>0.03710954606742156</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>1236</v>
+        <v>1443</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>宏亞</t>
+          <t>立益</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>586.1478862895519</v>
+        <v>688.1594924019631</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>26.45</v>
+        <v>23.9</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>65.02547086751376</v>
+        <v>58.07688968516396</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>23.81799621752979</v>
+        <v>14.70587132278922</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.7122080211546937</v>
+        <v>0.3586704142734938</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.07712421809013059</v>
+        <v>0.1460232762025273</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, foreign_buy_3d, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>1301</v>
+        <v>1307</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>三芳</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>584.510391279649</v>
+        <v>685.0035849691798</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>73.90000000000001</v>
+        <v>31.4</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>51.37300239578465</v>
+        <v>55.01923139320949</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>34.90041299167059</v>
+        <v>10.18333228781058</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.240108896620484</v>
+        <v>0.4595094381492864</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-0.9750328225436258</v>
+        <v>0.01055086256864443</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, rsi_strong, avoid_chase, hist_turn_positive, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>1434</v>
+        <v>1326</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>福懋</t>
+          <t>台化</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>561.5350119477084</v>
+        <v>661.3386574964164</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>19.05</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>50.91736873317329</v>
+        <v>52.08924711487083</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>33.86961337473438</v>
+        <v>31.56302749004429</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.2411420926644723</v>
+        <v>0.3071732137341162</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.1000909906636921</v>
+        <v>-0.5843604076979321</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>1558</v>
+        <v>1472</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>伸興</t>
+          <t>三洋實業</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>553.2402651869934</v>
+        <v>635.897035734474</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>108</v>
+        <v>89.2</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>41.75347224357601</v>
+        <v>53.2500411521592</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>22.85900052251849</v>
+        <v>6.075743595578839</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.8055357398716096</v>
+        <v>1.975534738788747</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-0.7805774648982009</v>
+        <v>-0.286437811127386</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, cci_momentum, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>1477</v>
+        <v>1456</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>怡華</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>534.4019379564074</v>
+        <v>618.0778618318739</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>206.5</v>
+        <v>15.45</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>56.76911027763534</v>
+        <v>58.9213742026065</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>33.33522949415202</v>
+        <v>21.22109419993154</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.6661681215624156</v>
+        <v>0.5742145694104217</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.3309809399986583</v>
+        <v>0.0221205691930198</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>1563</v>
+        <v>1560</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>巧新</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>519.868759252751</v>
+        <v>611.7059218726396</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>77.2</v>
+        <v>888</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,49 +1506,49 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>48.37684227749301</v>
+        <v>49.9228699649796</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>33.58434245334403</v>
+        <v>27.57223989098821</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.2055359409061496</v>
+        <v>0.6808788281873592</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-1.123222812365692</v>
+        <v>-16.18853063782765</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>1232</v>
+        <v>1453</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>大將</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>518.5010322252887</v>
+        <v>595.0231567290816</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>157.5</v>
+        <v>11.2</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>57.04108207769282</v>
+        <v>58.65707634031622</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>21.60283697531923</v>
+        <v>21.22011952338915</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.8577530788674693</v>
+        <v>0.8322407109329751</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.3715390863945235</v>
+        <v>0.03672381109736005</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>1303</v>
+        <v>1232</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>大統益</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>516.5309668339227</v>
+        <v>573.5010322252892</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>312</v>
+        <v>157.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>58.31853232335367</v>
+        <v>57.04108217410622</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>39.75180285871349</v>
+        <v>21.60283698516695</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.7101657592705942</v>
+        <v>0.8577530788674693</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-2.389913397078729</v>
+        <v>0.3715390861141769</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>1453</v>
+        <v>1341</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>大將</t>
+          <t>富林-KY</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>515.0231567290817</v>
+        <v>565.6783535181631</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>11.2</v>
+        <v>58.7</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>58.65707702667082</v>
+        <v>51.75289220789705</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>21.22011984362776</v>
+        <v>7.552677302803545</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.8322407109329751</v>
+        <v>2.121996232805038</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.03672381102727561</v>
+        <v>0.2026614536231299</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>macd_golden_cross, volume_break, avoid_chase, hist_turn_positive, foreign_buy_3d, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>1476</v>
+        <v>1516</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>儒鴻</t>
+          <t>川飛</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>510.6495410031008</v>
+        <v>551.2054873118915</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>322</v>
+        <v>22</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>61.65241749317113</v>
+        <v>69.43295382883923</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>35.05657181056816</v>
+        <v>26.64233689391699</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.5245776381302626</v>
+        <v>0.9906381116112182</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>1.749607729129175</v>
+        <v>1.098812014509556</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>1456</v>
+        <v>1225</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>怡華</t>
+          <t>福懋油</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>508.0778618318738</v>
+        <v>544.5231918337892</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>15.45</v>
+        <v>24.95</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>58.9213742026065</v>
+        <v>54.61004886742242</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>21.22109427398998</v>
+        <v>28.60756762074726</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.5742145694104217</v>
+        <v>1.33210273676917</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.02212056917900268</v>
+        <v>0.09800765097322398</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>1307</v>
+        <v>1110</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>三芳</t>
+          <t>東泥</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>495.0035849691801</v>
+        <v>542.5144516403461</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>31.4</v>
+        <v>15.05</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>55.01923139320949</v>
+        <v>56.39162463415662</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>10.18333230206181</v>
+        <v>38.4842337615931</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.4595094381492864</v>
+        <v>0.4538957855430882</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.01055086259667803</v>
+        <v>0.1182317693607111</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>聯成</t>
+          <t>國喬</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>488.176118552675</v>
+        <v>541.7370516241933</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>12.15</v>
+        <v>14.35</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>44.78420044249444</v>
+        <v>44.16603870600127</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>24.54365397625828</v>
+        <v>34.63017359767736</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.4822403790360304</v>
+        <v>0.2206517074519842</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.1136947401047776</v>
+        <v>-0.2659972571581402</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>1310</v>
+        <v>1535</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>台苯</t>
+          <t>中宇</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>475.1652053086448</v>
+        <v>539.7362293444802</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>9.199999999999999</v>
+        <v>46.05</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>45.50059735433258</v>
+        <v>55.4393568384406</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>38.38085655599668</v>
+        <v>18.53911080810969</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.369665926211944</v>
+        <v>0.5129894418934707</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.1177822241637698</v>
+        <v>0.02469134441896946</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, avoid_chase, foreign_buy_3d, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>1472</v>
+        <v>1301</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>三洋實業</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>470.8970357344741</v>
+        <v>524.510391279649</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>89.2</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>53.2500411369913</v>
+        <v>51.37300242109674</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>6.075743557546502</v>
+        <v>34.90041297838587</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.975534738788747</v>
+        <v>0.240108896620484</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.286437811127386</v>
+        <v>-0.9750328226697729</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>1443</v>
+        <v>1313</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>立益</t>
+          <t>聯成</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>468.1594924019632</v>
+        <v>523.176118552675</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>23.9</v>
+        <v>12.15</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>58.0768896963402</v>
+        <v>44.78420059124797</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>14.70587131553944</v>
+        <v>24.54365399742154</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.3586704142734938</v>
+        <v>0.4822403790360304</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.1460232762025273</v>
+        <v>-0.1136947401356155</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>1325</v>
+        <v>1419</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>恆大</t>
+          <t>新紡</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>461.9194970822019</v>
+        <v>513.2933979685289</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>26.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>46.73409451946274</v>
+        <v>52.29088325448016</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>24.74144663973683</v>
+        <v>13.69369861783109</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.1143545715175502</v>
+        <v>0.5572153169783731</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.269380156405556</v>
+        <v>0.0327446304344946</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, avoid_chase, hist_turn_positive, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>1304</v>
+        <v>1342</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>台聚</t>
+          <t>八貫</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>443.1211773796628</v>
+        <v>512.4305052000658</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>12.5</v>
+        <v>98.5</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>44.94178513268558</v>
+        <v>43.24151092298472</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>32.2857546134443</v>
+        <v>18.92295220718907</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.4300460342854988</v>
+        <v>0.4121842259415814</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.09506553097143697</v>
+        <v>-0.08367564587842113</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>1409</v>
+        <v>1530</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>新纖</t>
+          <t>亞崴</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>434.5277398618716</v>
+        <v>508.5082199634917</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>24.75</v>
+        <v>26.95</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>46.7527393309674</v>
+        <v>48.73359936309792</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>21.62015622247247</v>
+        <v>15.18321701111523</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.2758323761047834</v>
+        <v>0.3262335604658975</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.1366422043878775</v>
+        <v>0.02423751603433261</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>macd_golden_cross, avoid_chase, hist_turn_positive, foreign_buy_3d, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>1319</v>
+        <v>1325</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>恆大</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>433.3226827280473</v>
+        <v>501.9194970822019</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>80</v>
+        <v>26.8</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>46.34426487093627</v>
+        <v>46.73409459706966</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>24.18356263155937</v>
+        <v>24.74144676299839</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.4355806302604777</v>
+        <v>0.1143545715175502</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.1050783599832489</v>
+        <v>-0.2693801563775211</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>1419</v>
+        <v>1434</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>新紡</t>
+          <t>福懋</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>433.2933979685311</v>
+        <v>501.5350119477084</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>65.59999999999999</v>
+        <v>19.05</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>52.29088332008387</v>
+        <v>50.91736881582071</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>13.69369860263889</v>
+        <v>33.86961341379352</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.5572153169783731</v>
+        <v>0.2411420926644723</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.03274463065877331</v>
+        <v>-0.100090990691727</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>1418</v>
+        <v>1477</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>東華</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>430.5415127918785</v>
+        <v>494.4019379564074</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>17.9</v>
+        <v>206.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>44.13963450984452</v>
+        <v>56.76911038399261</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>34.88343501787275</v>
+        <v>33.33522948689854</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.7407475956588832</v>
+        <v>0.6661681215624156</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.07413333571257993</v>
+        <v>0.3309809402790007</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>1413</v>
+        <v>1558</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>宏洲</t>
+          <t>伸興</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>427.2327752404182</v>
+        <v>493.2402651869934</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>9.390000000000001</v>
+        <v>108</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>52.84204315654666</v>
+        <v>41.7534722471883</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>8.758252216654652</v>
+        <v>22.85900052251849</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.1299107608420363</v>
+        <v>0.8055357398716096</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>8.506270710868791e-05</v>
+        <v>-0.7805774649262296</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>1560</v>
+        <v>1319</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>416.7059218726396</v>
+        <v>488.3226827280473</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>888</v>
+        <v>80</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,49 +2460,49 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>49.92286996083875</v>
+        <v>46.34426495965612</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>27.5722398728353</v>
+        <v>24.18356272924211</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.6808788281873592</v>
+        <v>0.4355806302604777</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M38" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-16.18853063852842</v>
+        <v>-0.1050783602635943</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>1308</v>
+        <v>1413</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>亞聚</t>
+          <t>宏洲</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>416.592586702403</v>
+        <v>482.2327752404182</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>13.65</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>39.94013066800417</v>
+        <v>52.84204315654666</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>27.52289976155807</v>
+        <v>8.758252187308202</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.6384068392439981</v>
+        <v>0.1299107608420363</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.1216575465355764</v>
+        <v>8.506267907499102e-05</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, avoid_chase, hist_turn_positive, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>1323</v>
+        <v>1233</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>永裕</t>
+          <t>天仁</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>413.9273425113987</v>
+        <v>481.0797573731314</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>21.6</v>
+        <v>28.4</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>51.76760000909914</v>
+        <v>58.0716500549326</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>19.82380513853082</v>
+        <v>17.9771400724868</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.5061513121695868</v>
+        <v>0.2992041170486506</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.03211509692326972</v>
+        <v>0.05009544581962629</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>1516</v>
+        <v>1541</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>川飛</t>
+          <t>錩泰</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>411.2054873118914</v>
+        <v>480.0902639231797</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>22</v>
+        <v>19.75</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>69.43295376674682</v>
+        <v>49.87527785413217</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>26.64233681661767</v>
+        <v>9.955303409144467</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.9906381116112182</v>
+        <v>0.243527216785048</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>1.098812014687502</v>
+        <v>0.03496540350304854</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>1440</v>
+        <v>1476</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>南紡</t>
+          <t>儒鴻</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>410.2377725734499</v>
+        <v>460.6495410031008</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>13.7</v>
+        <v>322</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>48.13168076971264</v>
+        <v>61.65241747344645</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>21.21418758857504</v>
+        <v>35.05657188983024</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.2876834790534095</v>
+        <v>0.5245776381302626</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.03717354878304144</v>
+        <v>1.749607730110366</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>1341</v>
+        <v>1563</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>富林-KY</t>
+          <t>巧新</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>400.6783535181631</v>
+        <v>459.868759252751</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>58.7</v>
+        <v>77.2</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>51.75289220519225</v>
+        <v>48.37684223900369</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>7.552677302803546</v>
+        <v>33.58434244006641</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>2.121996232805038</v>
+        <v>0.2055359409061496</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.2026614537072418</v>
+        <v>-1.123222812269608</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>1465</v>
+        <v>1504</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>偉全</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>394.9498478545903</v>
+        <v>447.6899348025245</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>11.7</v>
+        <v>69.5</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,29 +2778,29 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>48.35904709856491</v>
+        <v>48.41643322375531</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>14.75016030793486</v>
+        <v>13.98802419110361</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.3729941623706042</v>
+        <v>0.4346908188200783</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M44" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.001872547190274673</v>
+        <v>-0.05504412272500059</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, liquidity_ok, stronger_than_market, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>386.8691645290983</v>
+        <v>436.8691645290983</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>10</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>44.4481825749285</v>
+        <v>44.44818336064286</v>
       </c>
       <c r="I45" s="2" t="n">
         <v>33.16714994279295</v>
@@ -2840,7 +2840,7 @@
         <v>0.4401056454459586</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.005743117429405142</v>
+        <v>-0.005743117513505695</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>1459</v>
+        <v>1423</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>聯發</t>
+          <t>利華</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>386.11374794065</v>
+        <v>436.4128014094595</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>17.9</v>
+        <v>35.1</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>56.64759304841003</v>
+        <v>51.8883339924814</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>62.6232151190183</v>
+        <v>8.181313102730206</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.09647386874800058</v>
+        <v>0.2871386096379252</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,11 +2902,11 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.1632974550072485</v>
+        <v>0.4850885679205837</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2923,7 @@
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>379.0767832138162</v>
+        <v>429.0767832138179</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>26.5</v>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>46.95093046160441</v>
+        <v>46.95093089654779</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>23.54439120172596</v>
+        <v>23.54439127817047</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>0.5081416199260037</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.02863537509504392</v>
+        <v>-0.02863537506700745</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>1535</v>
+        <v>1210</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>中宇</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>374.7362293444801</v>
+        <v>427.6177689027334</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>46.05</v>
+        <v>51</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,49 +2990,49 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>55.43935700097482</v>
+        <v>40.31167718880093</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>18.5391107565326</v>
+        <v>19.75324288985084</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.5129894418934707</v>
+        <v>0.5878612992272083</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M48" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.02469134439093207</v>
+        <v>0.004287694525769992</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, liquidity_ok, kd_golden_cross, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>1210</v>
+        <v>1532</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>勤美</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>372.6177689027334</v>
+        <v>424.0338310244668</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>51</v>
+        <v>22.15</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>40.31167700889064</v>
+        <v>51.17331876976049</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>19.7532428850951</v>
+        <v>23.25698526564837</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.5878612992272083</v>
+        <v>0.5787373252166153</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.004287694637908235</v>
+        <v>0.0849020482796819</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>1532</v>
+        <v>1219</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>勤美</t>
+          <t>福壽</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>369.0338310244668</v>
+        <v>419.3165888437493</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>22.15</v>
+        <v>11.35</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>51.17331866171595</v>
+        <v>55.41300231303534</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>23.25698522377256</v>
+        <v>12.24641870885859</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.5787373252166153</v>
+        <v>1.255132984759711</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.08490204836378451</v>
+        <v>0.01809223702731036</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>1215</v>
+        <v>1525</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>江申</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>368.7307819973261</v>
+        <v>419.088618161349</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>105</v>
+        <v>64</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>44.0909276123027</v>
+        <v>51.92814418678937</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>15.60302849276408</v>
+        <v>7.588747097309369</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.6956486385325303</v>
+        <v>0.1856701226831789</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.1021824750441883</v>
+        <v>0.3264572227834138</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>1455</v>
+        <v>1104</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>集盛</t>
+          <t>環泥</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>367.5964425219917</v>
+        <v>415.1816593987203</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>9.56</v>
+        <v>26.95</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,49 +3202,49 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>41.74119114014212</v>
+        <v>52.07781327873834</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>27.0823349270683</v>
+        <v>20.06239649790996</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.2441621216430813</v>
+        <v>0.6204499993500532</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M52" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.06957102754417696</v>
+        <v>0.01047887572538175</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>avoid_chase, adx_trending, stronger_than_market, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>1305</v>
+        <v>1310</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>華夏</t>
+          <t>台苯</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>360.2092944292863</v>
+        <v>415.1652053086448</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>12.35</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>45.27662450346372</v>
+        <v>45.50059739085575</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>28.98388277292551</v>
+        <v>38.38085652903516</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.2680010445169915</v>
+        <v>0.369665926211944</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.09211098493999156</v>
+        <v>-0.1177822241974095</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>1460</v>
+        <v>1410</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>宏遠</t>
+          <t>南染</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>355.4684544504765</v>
+        <v>405.0278804338221</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>6</v>
+        <v>23.7</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>30.23605556858452</v>
+        <v>44.85029501299947</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>29.48280523297741</v>
+        <v>9.318977844395699</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>2.91239098657363</v>
+        <v>0.3033898350005256</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.004828408920368593</v>
+        <v>0.05329831589144224</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>1225</v>
+        <v>1470</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>福懋油</t>
+          <t>大統新創</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>354.5231918337891</v>
+        <v>400.6023420423884</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>24.95</v>
+        <v>23.8</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>54.61004897931525</v>
+        <v>51.0995959828546</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>28.60756776184585</v>
+        <v>10.73525333544206</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.33210273676917</v>
+        <v>0.7249060924411947</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.09800765090313954</v>
+        <v>0.2442270351723059</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>1470</v>
+        <v>1522</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>大統新創</t>
+          <t>堤維西</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>350.6023420423884</v>
+        <v>386.6703584627939</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>23.8</v>
+        <v>26.75</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>51.09959603505124</v>
+        <v>52.07092568795527</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>10.73525335683843</v>
+        <v>12.45052463149521</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.7249060924411947</v>
+        <v>1.150611267461744</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.244227034807864</v>
+        <v>0.04357208320722421</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>1342</v>
+        <v>1435</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>八貫</t>
+          <t>中福</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>347.4305052000659</v>
+        <v>385.6076364081443</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>98.5</v>
+        <v>21.35</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>43.24151069890355</v>
+        <v>51.65169706136457</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>18.92295226553459</v>
+        <v>5.566977045231849</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.4121842259415814</v>
+        <v>0.3122566787488253</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.08367564548592887</v>
+        <v>0.3608142901362427</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>stronger_than_market, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>1530</v>
+        <v>1304</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>亞崴</t>
+          <t>台聚</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>343.5082199634917</v>
+        <v>383.1211773796628</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>26.95</v>
+        <v>12.5</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>48.73359942577747</v>
+        <v>44.94178515172417</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>15.18321700576585</v>
+        <v>32.28575455097526</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.3262335604658975</v>
+        <v>0.4300460342854988</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.02423751599227908</v>
+        <v>-0.09506553097143697</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, mfi_strong</t>
+          <t>avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>1522</v>
+        <v>1316</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>堤維西</t>
+          <t>上曜</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>336.670358462794</v>
+        <v>381.6391767650424</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>26.75</v>
+        <v>10.5</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>52.0709254128835</v>
+        <v>50.38582196735494</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>12.45052456906537</v>
+        <v>14.52638726804596</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.150611267461744</v>
+        <v>0.8533382628777727</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.04357208322124182</v>
+        <v>0.02048658229145396</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>1526</v>
+        <v>1229</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>日馳</t>
+          <t>聯華</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>335.7134592870605</v>
+        <v>381.5538733895066</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>15.85</v>
+        <v>40</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,49 +3626,49 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>52.2229721318986</v>
+        <v>45.36278432724458</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>27.29937245215877</v>
+        <v>16.61656693824569</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.6453524207177652</v>
+        <v>0.4810514550077166</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M60" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.1577658273762767</v>
+        <v>-0.02738929877373031</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, liquidity_ok, kd_golden_cross, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>1314</v>
+        <v>1468</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>中石化</t>
+          <t>昶和</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>328.8903274120658</v>
+        <v>379.4632432409553</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>8.24</v>
+        <v>13.3</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>39.64834326630314</v>
+        <v>51.51789462216617</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>29.28061885452529</v>
+        <v>8.5444606101809</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.4013798953624997</v>
+        <v>0.5213971457230537</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.1082726975110105</v>
+        <v>0.01225646659957578</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, foreign_buy_3d, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>台達化</t>
+          <t>亞聚</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>327.4819556664684</v>
+        <v>376.592586702403</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>13</v>
+        <v>13.65</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>37.64088597131151</v>
+        <v>39.94013070117194</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>28.61473473054357</v>
+        <v>27.52289978269573</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.7314592612901785</v>
+        <v>0.6384068392439981</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.1665305378109619</v>
+        <v>-0.1216575465495925</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>1316</v>
+        <v>1409</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>上曜</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>326.6391767650424</v>
+        <v>374.5277398618716</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>10.5</v>
+        <v>24.75</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>50.38582199237251</v>
+        <v>46.75273934527728</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>14.52638703094421</v>
+        <v>21.62015630441747</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.8533382628777727</v>
+        <v>0.2758323761047834</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.02048658233350373</v>
+        <v>-0.1366422044159121</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>1229</v>
+        <v>1418</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>聯華</t>
+          <t>東華</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>326.5538733895069</v>
+        <v>370.5415127918785</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>40</v>
+        <v>17.9</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>45.3627842207499</v>
+        <v>44.13963464320042</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>16.61656690754261</v>
+        <v>34.88343512328113</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.4810514550077166</v>
+        <v>0.7407475956588832</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.02738929882980348</v>
+        <v>-0.07413333572659532</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>1110</v>
+        <v>1463</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>東泥</t>
+          <t>強盛新</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>322.5144516403461</v>
+        <v>357.4533499580846</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>15.05</v>
+        <v>17.75</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>56.39162463415662</v>
+        <v>52.85679182213445</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>38.48423374010224</v>
+        <v>13.71670585502231</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.4538957855430882</v>
+        <v>0.2843585814613998</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.1182317693466909</v>
+        <v>-0.01459886805174648</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>1402</v>
+        <v>1436</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>華友聯</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>321.1038570500211</v>
+        <v>354.6806430130342</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>28.35</v>
+        <v>35.8</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>48.00171038795186</v>
+        <v>45.13800212550157</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>19.14396838329136</v>
+        <v>12.88397762721356</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.3547362951299028</v>
+        <v>1.377628546488266</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.05601346965186207</v>
+        <v>0.03040932351554526</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>1451</v>
+        <v>1323</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>年興</t>
+          <t>永裕</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>320.9808677116674</v>
+        <v>353.9273425113987</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>17</v>
+        <v>21.6</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>44.33105007214166</v>
+        <v>51.7675999817266</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>13.39075029945919</v>
+        <v>19.82380513853082</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.4346335291075634</v>
+        <v>0.5061513121695868</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.0003436197810774977</v>
+        <v>-0.03211509690925107</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>1457</v>
+        <v>1513</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>宜進</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>316.9313000373654</v>
+        <v>351.795862758491</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>14.4</v>
+        <v>157</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,49 +4050,49 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>48.97293207244823</v>
+        <v>33.54694205911098</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>18.79328364044324</v>
+        <v>15.80126405061372</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.6322750310030385</v>
+        <v>0.6901288062917414</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M68" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.01304401508849403</v>
+        <v>-0.9960971759274748</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>1233</v>
+        <v>1340</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>天仁</t>
+          <t>勝悅-KY</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>316.0797573731314</v>
+        <v>351.2859216956492</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>28.4</v>
+        <v>5.05</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>58.0716500549326</v>
+        <v>44.07063501721755</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>17.97714003541236</v>
+        <v>11.21238924221118</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.2992041170486506</v>
+        <v>2.028592169564922</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.05009544581962629</v>
+        <v>-0.002304376245523515</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>1541</v>
+        <v>1442</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>錩泰</t>
+          <t>名軒</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>315.0902639231813</v>
+        <v>350.2928813954104</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>19.75</v>
+        <v>26.1</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>49.8752778745915</v>
+        <v>37.49542336176759</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>9.955303409144467</v>
+        <v>32.64756248455994</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.243527216785048</v>
+        <v>0.3008601899345437</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.03496540330681282</v>
+        <v>0.05466256130361735</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>1463</v>
+        <v>1440</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>強盛新</t>
+          <t>南紡</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>307.4533499580846</v>
+        <v>350.2377725734499</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>17.75</v>
+        <v>13.7</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>52.85679170934116</v>
+        <v>48.1316808084</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>13.71670590455269</v>
+        <v>21.21418766303899</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.2843585814613998</v>
+        <v>0.2876834790534095</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.01459886803773</v>
+        <v>-0.03717354881107462</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>1514</v>
+        <v>1474</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>弘裕</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>303.3776899939789</v>
+        <v>344.3471294602801</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>97</v>
+        <v>10</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>37.47867973187045</v>
+        <v>50.47307193946105</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>13.32513573076321</v>
+        <v>10.75313864036433</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.7424708707982308</v>
+        <v>0.2047336756620847</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.4866017355699193</v>
+        <v>0.003113029778695514</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>1436</v>
+        <v>1314</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>華友聯</t>
+          <t>中石化</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>299.6806430130341</v>
+        <v>343.8903274120658</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>35.8</v>
+        <v>8.24</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>45.13800399640127</v>
+        <v>39.64834350388002</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>12.8839758566156</v>
+        <v>29.28061883031623</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.377628546488266</v>
+        <v>0.4013798953624997</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.03040932270256003</v>
+        <v>-0.1082726975166161</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>1513</v>
+        <v>1256</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>鮮活果汁-KY</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>296.795862758491</v>
+        <v>343.4153412305618</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>33.54694207448024</v>
+        <v>42.79065236593041</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>15.80126394749298</v>
+        <v>10.90458800783675</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.6901288062917414</v>
+        <v>0.9979953434928192</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.9960971756471553</v>
+        <v>0.1178153274212943</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>1213</v>
+        <v>1465</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>大飲</t>
+          <t>偉全</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>296.4519863220901</v>
+        <v>334.9498478545903</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>34.59339080739987</v>
+        <v>48.35904699178703</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>10.23864448355159</v>
+        <v>14.75016036927247</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0</v>
+        <v>0.3729941623706042</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.382312852704136</v>
+        <v>0.001872547204289525</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>1442</v>
+        <v>1459</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>名軒</t>
+          <t>聯發</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>295.2928813954083</v>
+        <v>326.11374794065</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>26.1</v>
+        <v>17.9</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>37.49542399317668</v>
+        <v>56.64759302400883</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>32.64756213276312</v>
+        <v>62.62321526187403</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.3008601899345437</v>
+        <v>0.09647386874800058</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.05466256135968295</v>
+        <v>-0.1632974550072485</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>1256</v>
+        <v>1512</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>鮮活果汁-KY</t>
+          <t>瑞利</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>293.4153412305618</v>
+        <v>320.9173866483644</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>166</v>
+        <v>6.33</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>42.7906529530449</v>
+        <v>53.51599482131392</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>10.90458803575331</v>
+        <v>17.48752703205917</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.9979953434928192</v>
+        <v>0.5315914026259989</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.1178153248982268</v>
+        <v>0.0128288227067288</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, stronger_than_market, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>1474</v>
+        <v>1215</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>弘裕</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>289.3471294602801</v>
+        <v>308.7307819973287</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>10</v>
+        <v>105</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>50.47307232970604</v>
+        <v>44.09092795165244</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>10.75313852245356</v>
+        <v>15.60302856744529</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.2047336756620847</v>
+        <v>0.6956486385325303</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.003113029764678735</v>
+        <v>0.1021824744834975</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>1452</v>
+        <v>1455</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>宏益</t>
+          <t>集盛</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>287.4904083375931</v>
+        <v>307.5964425219917</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>10.85</v>
+        <v>9.56</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>49.22918022261155</v>
+        <v>41.74119114014212</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>16.73652189854198</v>
+        <v>27.08233492954254</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.564167662560098</v>
+        <v>0.2441621216430813</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.03123117020946144</v>
+        <v>-0.06957102753296253</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>1504</v>
+        <v>1305</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>華夏</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>277.6899348025245</v>
+        <v>300.2092944292864</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>69.5</v>
+        <v>12.35</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>48.41643299897807</v>
+        <v>45.27662443990903</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>13.9880241545212</v>
+        <v>28.9838827204023</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.4346908188200783</v>
+        <v>0.2680010445169915</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.05504412308943073</v>
+        <v>-0.09211098488392333</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>1435</v>
+        <v>1460</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>中福</t>
+          <t>宏遠</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>275.6076364081443</v>
+        <v>295.4684544504757</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>21.35</v>
+        <v>6</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>51.65170908860745</v>
+        <v>30.23605552497214</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>5.566976758321026</v>
+        <v>29.4828052071381</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.3122566787488253</v>
+        <v>2.91239098657363</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.3608142884782763</v>
+        <v>0.004828408914761578</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>volume_break, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>1339</v>
+        <v>1521</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>昭輝</t>
+          <t>大億</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>268.5973876054961</v>
+        <v>293.0690466381392</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>41.3</v>
+        <v>25.4</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>36.12345620099727</v>
+        <v>48.59882282597293</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>31.85783717696624</v>
+        <v>21.48762981373356</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.4940775822764787</v>
+        <v>0.8466824343985258</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.05754700694684134</v>
+        <v>-0.05362921979283605</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>1568</v>
+        <v>1203</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>倉佑</t>
+          <t>味王</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>266.3131828978113</v>
+        <v>286.7222418907851</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>28.4</v>
+        <v>43.7</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>36.77537528723105</v>
+        <v>51.46715881616385</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>25.56854055613568</v>
+        <v>8.679079856646696</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.3471085483300073</v>
+        <v>0.4201045810708718</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.2762896067372443</v>
+        <v>0.1343936828310896</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>瑞利</t>
+          <t>力山</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>265.9173866483644</v>
+        <v>277.1142152879248</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>6.33</v>
+        <v>27.75</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>53.51599475113794</v>
+        <v>40.2202039505621</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>17.48752703962701</v>
+        <v>9.453542368029009</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.5315914026259989</v>
+        <v>0.543886225397771</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.01282882270953175</v>
+        <v>0.006652091790675274</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>1473</v>
+        <v>1526</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>日馳</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>264.9514528141752</v>
+        <v>275.7134592870605</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>18.75</v>
+        <v>15.85</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>31.84689491557361</v>
+        <v>52.22297206694639</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>39.01269975392596</v>
+        <v>27.29937245422219</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.3101439287241789</v>
+        <v>0.6453524207177652</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.01420229416016322</v>
+        <v>0.1577658273762767</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>1217</v>
+        <v>1467</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>愛之味</t>
+          <t>南緯</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>257.6385726454172</v>
+        <v>270.0549650709639</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>9.66</v>
+        <v>7.85</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>31.56808332358234</v>
+        <v>40.51488441277082</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>30.31104551318092</v>
+        <v>13.07187286151512</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.365147208364861</v>
+        <v>0.2725788210559094</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.02297036998783913</v>
+        <v>-0.02165181615763398</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>1437</v>
+        <v>1309</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>勤益控</t>
+          <t>台達化</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>248.0018902867054</v>
+        <v>267.4819556664684</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>31.5</v>
+        <v>13</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>49.42806291611831</v>
+        <v>37.6408859876128</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>14.59650889479922</v>
+        <v>28.61473475805394</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.5782898584248687</v>
+        <v>0.7314592612901785</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.04276952651084978</v>
+        <v>-0.1665305378109619</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>1423</v>
+        <v>1503</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>利華</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>246.4128014094595</v>
+        <v>267.3820369711135</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>35.1</v>
+        <v>188</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,49 +5110,49 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>51.8883339932843</v>
+        <v>37.4438261876866</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>8.181312996662001</v>
+        <v>9.318192146978403</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.2871386096379252</v>
+        <v>0.7607842441907648</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L88" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M88" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.4850885678925499</v>
+        <v>-0.7977563416982105</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>avoid_chase, liquidity_ok, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>1104</v>
+        <v>1402</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>245.1816593987204</v>
+        <v>261.1038570500211</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>26.95</v>
+        <v>28.35</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>52.07781309526046</v>
+        <v>48.00171048807142</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>20.06239630161161</v>
+        <v>19.14396827248983</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.6204499993500532</v>
+        <v>0.3547362951299028</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.01047887583751767</v>
+        <v>-0.05601346973596227</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>1231</v>
+        <v>1451</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>聯華食</t>
+          <t>年興</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>242.0655526737721</v>
+        <v>260.9808677116675</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>73.09999999999999</v>
+        <v>17</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>17.31021340835505</v>
+        <v>44.33105014286756</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>44.0046324233907</v>
+        <v>13.39075030374685</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.9758573443403299</v>
+        <v>0.4346335291075634</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.3429282062649484</v>
+        <v>-0.0003436197950979214</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>1537</v>
+        <v>1108</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>廣隆</t>
+          <t>幸福</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>241.7390120698364</v>
+        <v>259.1856026883115</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>113</v>
+        <v>10.95</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>43.44278822064948</v>
+        <v>32.8661523936659</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>26.87726040520165</v>
+        <v>34.58289032022842</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.7746118377539057</v>
+        <v>1.176986015203389</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.01394876581863269</v>
+        <v>0.01073483143200152</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>1338</v>
+        <v>1457</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>廣華-KY</t>
+          <t>宜進</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>240.2599034143909</v>
+        <v>256.9313000373652</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>14.2</v>
+        <v>14.4</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>37.48567739255921</v>
+        <v>48.97293213847307</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>21.62652100147518</v>
+        <v>18.79328364044324</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1.87280557523734</v>
+        <v>0.6322750310030385</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.06230410263930208</v>
+        <v>0.01304401507447491</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>1410</v>
+        <v>1432</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>南染</t>
+          <t>大魯閣</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>240.0278804338221</v>
+        <v>253.615759548656</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>23.7</v>
+        <v>14.95</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>44.85029498791995</v>
+        <v>45.79822889107028</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>9.318977756074226</v>
+        <v>16.39808450147892</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.3033898350005256</v>
+        <v>1.031039797491094</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.05329831582135569</v>
+        <v>-0.001578444929719799</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>1521</v>
+        <v>1514</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>大億</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>238.0690466381392</v>
+        <v>243.3776899940023</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>25.4</v>
+        <v>97</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>48.59882231665034</v>
+        <v>37.47867981475815</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>21.48762981861004</v>
+        <v>13.32513573095349</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.8466824343985258</v>
+        <v>0.7424708707982308</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.05362921979283605</v>
+        <v>-0.4866017358502577</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>1219</v>
+        <v>1213</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>福壽</t>
+          <t>大飲</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>229.3165888437493</v>
+        <v>236.4519863220901</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>11.35</v>
+        <v>0</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>55.41300225514883</v>
+        <v>34.59339081958242</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>12.24641870581865</v>
+        <v>10.23864448349791</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1.255132984759711</v>
+        <v>0</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.01809223705534514</v>
+        <v>-0.3823128527882378</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>1525</v>
+        <v>1536</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>江申</t>
+          <t>和大</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>229.088618161349</v>
+        <v>232.9085029222027</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>64</v>
+        <v>44.35</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>51.92814418402659</v>
+        <v>40.74426436182086</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>7.588747083780103</v>
+        <v>23.65176535053737</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.1856701226831789</v>
+        <v>0.9570674039428774</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.3264572226152146</v>
+        <v>0.09605697852635053</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>1515</v>
+        <v>1540</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>力山</t>
+          <t>喬福</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>227.1142152879247</v>
+        <v>228.0213067159521</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>27.75</v>
+        <v>18.85</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>40.22020399820992</v>
+        <v>45.42248930021477</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>9.453542418333988</v>
+        <v>13.02030376161437</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.543886225397771</v>
+        <v>0.4849237330639702</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.006652091762640699</v>
+        <v>0.03017148283899906</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>1441</v>
+        <v>1452</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>大東</t>
+          <t>宏益</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>220.5114281328246</v>
+        <v>227.4904083375932</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>9.59</v>
+        <v>10.85</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>51.74753368818065</v>
+        <v>49.22918025360177</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>27.2375880272463</v>
+        <v>16.73652192102965</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.3168198025233132</v>
+        <v>1.564167662560098</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.05767217129200829</v>
+        <v>0.03123117023749489</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>volume_break, avoid_chase, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>1467</v>
+        <v>1414</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>南緯</t>
+          <t>東和</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>220.0549650709639</v>
+        <v>216.6905968996805</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>7.85</v>
+        <v>17.4</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>40.51488448752429</v>
+        <v>45.33805323771538</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>13.07187289241911</v>
+        <v>15.2861741566407</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.2725788210559094</v>
+        <v>0.5083370635631155</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.02165181617725781</v>
+        <v>0.02974012004872387</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>1517</v>
+        <v>1506</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>利奇</t>
+          <t>正道</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>215.953944075085</v>
+        <v>209.3976747801371</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>10.2</v>
+        <v>9.49</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>39.68709897877501</v>
+        <v>33.59044493903075</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>23.22236107139134</v>
+        <v>17.1909559377728</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.4286957487779588</v>
+        <v>0.4694757756751191</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.01522535172440287</v>
+        <v>0.006221754270265792</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>1468</v>
+        <v>1339</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>昶和</t>
+          <t>昭輝</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>214.4632432409554</v>
+        <v>208.5973876054961</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>13.3</v>
+        <v>41.3</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>51.51789462216617</v>
+        <v>36.12345626843312</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>8.544460499739799</v>
+        <v>31.85783725807296</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.5213971457230537</v>
+        <v>0.4940775822764787</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.01225646655752435</v>
+        <v>-0.05754700691880871</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>1109</v>
+        <v>1568</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>信大</t>
+          <t>倉佑</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>213.4335398538351</v>
+        <v>206.3131828978113</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>13</v>
+        <v>28.4</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>35.3569677903785</v>
+        <v>36.77537535079838</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>36.57513702373948</v>
+        <v>25.5685405612969</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>1.256568904957373</v>
+        <v>0.3471085483300073</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.0006430237418362239</v>
+        <v>-0.2762896066951961</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>1503</v>
+        <v>1473</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>台南</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>212.3820369711137</v>
+        <v>204.9514528141752</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>188</v>
+        <v>18.75</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>37.44382613384929</v>
+        <v>31.84689521975803</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>9.318192239931648</v>
+        <v>39.01269974045839</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.7607842441907648</v>
+        <v>0.3101439287241789</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.7977563408572141</v>
+        <v>0.01420229410409399</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>1519</v>
+        <v>1447</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>力鵬</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>210.8925054466898</v>
+        <v>202.9905988079465</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>563</v>
+        <v>6.2</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>27.13271874627243</v>
+        <v>38.42260155850132</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>17.51325973964758</v>
+        <v>19.58624164121619</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.9727751816514478</v>
+        <v>0.3807071469822879</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-10.286963325774</v>
+        <v>-0.02373141009866928</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>1108</v>
+        <v>1537</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>幸福</t>
+          <t>廣隆</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>209.1856026883116</v>
+        <v>201.7390120698364</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>10.95</v>
+        <v>113</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>32.86615245027444</v>
+        <v>43.44278807711429</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>34.58289032022843</v>
+        <v>26.87726053485324</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>1.176986015203389</v>
+        <v>0.7746118377539057</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.01073483143200152</v>
+        <v>-0.0139487655383006</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>1203</v>
+        <v>1446</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>味王</t>
+          <t>宏和</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>206.7222418907842</v>
+        <v>199.8965845363869</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>43.7</v>
+        <v>13.35</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>51.46715877915079</v>
+        <v>43.39564652955436</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>8.679079842870129</v>
+        <v>12.89240515163858</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.4201045810708718</v>
+        <v>0.3258550860843653</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.1343936829151882</v>
+        <v>-0.001246661603209569</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>1539</v>
+        <v>1217</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>巨庭</t>
+          <t>愛之味</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>203.5373318765024</v>
+        <v>197.6385726454163</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>15.25</v>
+        <v>9.66</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>33.57107286908251</v>
+        <v>31.56808342231258</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>28.24679457580575</v>
+        <v>30.31104568235932</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.5911012659911364</v>
+        <v>1.365147208364861</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.02289227001034212</v>
+        <v>-0.0229703700158702</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>1464</v>
+        <v>1220</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>得力</t>
+          <t>台榮</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>203.035351734539</v>
+        <v>197.1197491968201</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>9.880000000000001</v>
+        <v>10.75</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>38.44516179011093</v>
+        <v>42.98713123143286</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>28.01145881808836</v>
+        <v>17.76657712131568</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.7862761644309579</v>
+        <v>0.2876912838705312</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.001809643330611871</v>
+        <v>-0.01474258797293882</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>1414</v>
+        <v>1438</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>東和</t>
+          <t>三地開發</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>201.6905968996805</v>
+        <v>191.3607400744491</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>17.4</v>
+        <v>21.55</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>45.33805313751739</v>
+        <v>47.09962142596607</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>15.28617410703785</v>
+        <v>6.50779565296962</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.5083370635631155</v>
+        <v>0.1726561818657519</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.02974011997665346</v>
+        <v>0.01238693662560975</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>1529</v>
+        <v>1437</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>樂事綠能</t>
+          <t>勤益控</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>189.7861688125832</v>
+        <v>188.0018902867054</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>14.4</v>
+        <v>31.5</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>32.57764213450454</v>
+        <v>49.42806289990338</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>24.55553823729516</v>
+        <v>14.59650885347235</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.4337955021474542</v>
+        <v>0.5782898584248687</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.04072652385377457</v>
+        <v>0.04276952652486821</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>1340</v>
+        <v>1231</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>勝悅-KY</t>
+          <t>聯華食</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>186.2859216956492</v>
+        <v>182.0655526737722</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>5.05</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>44.0706351608566</v>
+        <v>17.31021346169716</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>11.21238923522773</v>
+        <v>44.0046323532888</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>2.028592169564922</v>
+        <v>0.9758573443403299</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.002304376253934114</v>
+        <v>-0.3429282068256239</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>1538</v>
+        <v>1338</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>正峰</t>
+          <t>廣華-KY</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>179.2664645562843</v>
+        <v>180.2599034143909</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>0</v>
+        <v>14.2</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>43.30521639661762</v>
+        <v>37.48567742535424</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>16.35063186626233</v>
+        <v>21.62652104386553</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.01295901417244914</v>
+        <v>1.87280557523734</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.6857731316587644</v>
+        <v>-0.06230410261126867</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>volume_break, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>1536</v>
+        <v>1109</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>和大</t>
+          <t>信大</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>177.9085029222026</v>
+        <v>173.4335398538352</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>44.35</v>
+        <v>13</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>40.74426412832897</v>
+        <v>35.35696760883403</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>23.65176531474998</v>
+        <v>36.57513702373948</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.9570674039428774</v>
+        <v>1.256568904957373</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.09605697849832284</v>
+        <v>0.0006430237558531227</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>1540</v>
+        <v>1531</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>喬福</t>
+          <t>高林股</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>173.0213067159521</v>
+        <v>171.5451619632084</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>18.85</v>
+        <v>11.45</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>45.42248930021477</v>
+        <v>43.45904283469944</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>13.02030373851781</v>
+        <v>19.97486064765864</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.4849237330639702</v>
+        <v>0.5911082157928051</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.03017148283899906</v>
+        <v>0.0248069364506342</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>1527</v>
+        <v>1441</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>鑽全</t>
+          <t>大東</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>166.0123381451066</v>
+        <v>160.5114281328247</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>32.1</v>
+        <v>9.59</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>39.74037156116335</v>
+        <v>51.74753369259551</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>12.85515267806219</v>
+        <v>27.23758804555947</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>1.058787611950304</v>
+        <v>0.3168198025233132</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.03791455354577146</v>
+        <v>-0.05767217131424937</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>1506</v>
+        <v>1517</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>正道</t>
+          <t>利奇</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>159.397674780137</v>
+        <v>155.953944075085</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>9.49</v>
+        <v>10.2</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,16 +6594,16 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>33.59044395797167</v>
+        <v>39.68709892410556</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>17.19095597783437</v>
+        <v>23.2223612223018</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.4694757756751191</v>
+        <v>0.4286957487779588</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.006221754256249643</v>
+        <v>0.01522535175243692</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>1444</v>
+        <v>1519</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>力麗</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>159.1871469061189</v>
+        <v>150.8925054466895</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>6.56</v>
+        <v>563</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>35.35073998917814</v>
+        <v>27.13271880744047</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>18.00482442847254</v>
+        <v>17.51325957269129</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.4021844821567327</v>
+        <v>0.9727751816514478</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.02965898336871696</v>
+        <v>-10.28696332773645</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>1218</v>
+        <v>1539</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>泰山</t>
+          <t>巨庭</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>154.9073648411257</v>
+        <v>143.5373318765023</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>14</v>
+        <v>15.25</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>42.5266470662882</v>
+        <v>33.57107286908251</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>9.356008065586069</v>
+        <v>28.24679465012494</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.4468132213478772</v>
+        <v>0.5911012659911364</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.0611294723304782</v>
+        <v>-0.02289227005239217</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>1447</v>
+        <v>1464</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>力鵬</t>
+          <t>得力</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>152.9905988079464</v>
+        <v>143.035351734539</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>6.2</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>38.42260158993536</v>
+        <v>38.44516198350703</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>19.58624164121619</v>
+        <v>28.01145886592182</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.3807071469822879</v>
+        <v>0.7862761644309579</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.02373141009025855</v>
+        <v>0.001809643330611871</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>1454</v>
+        <v>1529</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>台富</t>
+          <t>樂事綠能</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>152.8082701214332</v>
+        <v>129.786168812583</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>12</v>
+        <v>14.4</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,16 +6806,16 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>40.41731720147332</v>
+        <v>32.57764214597404</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>17.76379470526431</v>
+        <v>24.55553824215993</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>1.295788404052761</v>
+        <v>0.4337955021474542</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.07156608986199742</v>
+        <v>-0.04072652392385978</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>1466</v>
+        <v>1417</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>聚隆</t>
+          <t>嘉裕</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>151.1766696445228</v>
+        <v>128.8254372304142</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>14.5</v>
+        <v>8.09</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,16 +6859,16 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>46.69122682159213</v>
+        <v>42.69079531398913</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>13.73573028122945</v>
+        <v>11.90022847071826</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.6278983491003524</v>
+        <v>0.6149223717881894</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.05336976674022387</v>
+        <v>0.001126261884367902</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>1446</v>
+        <v>1471</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>宏和</t>
+          <t>首利</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>149.8965845363865</v>
+        <v>127.8112885483737</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>13.35</v>
+        <v>9.07</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,16 +6912,16 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>43.39564623341687</v>
+        <v>39.95438533130856</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>12.89240513274897</v>
+        <v>14.71328555673955</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.3258550860843653</v>
+        <v>0.7052728901524269</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.001246661449022329</v>
+        <v>0.003955206841426667</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>1582</v>
+        <v>1538</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>信錦</t>
+          <t>正峰</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>147.1508343881989</v>
+        <v>119.2664645562843</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>69.7</v>
+        <v>0</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>44.5501926029391</v>
+        <v>43.305216389645</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>13.61174410238409</v>
+        <v>16.35063188170388</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.8072010357454377</v>
+        <v>0.01295901417244914</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.02941682395801343</v>
+        <v>-0.6857731316587644</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>台榮</t>
+          <t>泰山</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>147.1197491968201</v>
+        <v>114.9073648411256</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>10.75</v>
+        <v>14</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,16 +7018,16 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>42.98713123143286</v>
+        <v>42.52664708237133</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>17.76657708344195</v>
+        <v>9.35600811685538</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.2876912838705312</v>
+        <v>0.4468132213478772</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.01474258798695693</v>
+        <v>-0.0611294723444949</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>1438</v>
+        <v>1466</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>三地開發</t>
+          <t>聚隆</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>141.3607400744491</v>
+        <v>111.1766696445226</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>21.55</v>
+        <v>14.5</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,16 +7071,16 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>47.09962119902461</v>
+        <v>46.69122635669537</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>6.507795165768712</v>
+        <v>13.73573036035745</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.1726561818657519</v>
+        <v>0.6278983491003524</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L125" s="2" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>0.01238693690595165</v>
+        <v>0.05336976702056304</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>1324</v>
+        <v>1527</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>地球</t>
+          <t>鑽全</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>141.0038828109205</v>
+        <v>106.0123381451068</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>9.779999999999999</v>
+        <v>32.1</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,16 +7124,16 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>36.02925058903507</v>
+        <v>39.74037145023856</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>16.58413635229982</v>
+        <v>12.85515267195254</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>1.176250218738473</v>
+        <v>1.058787611950304</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L126" s="2" t="n">
         <v>0</v>
@@ -7142,31 +7142,31 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.009726715566857155</v>
+        <v>-0.03791455350371645</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>1531</v>
+        <v>1444</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>高林股</t>
+          <t>力麗</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>121.5451619632085</v>
+        <v>99.18714690611884</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>11.45</v>
+        <v>6.56</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,16 +7177,16 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>43.45904283469944</v>
+        <v>35.35074000217672</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>19.97486058760924</v>
+        <v>18.00482445713417</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.5911082157928051</v>
+        <v>0.4021844821567327</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L127" s="2" t="n">
         <v>0</v>
@@ -7195,31 +7195,31 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>0.02480693642260051</v>
+        <v>-0.02965898337712777</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>1227</v>
+        <v>1454</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>佳格</t>
+          <t>台富</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>113.9045397106975</v>
+        <v>92.80827012143278</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>27.75</v>
+        <v>12</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,13 +7230,13 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>43.40837105402846</v>
+        <v>40.41731720147332</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>17.7731751731255</v>
+        <v>17.7637947251959</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.6902961814515265</v>
+        <v>1.295788404052761</v>
       </c>
       <c r="K128" s="2" t="n">
         <v>0</v>
@@ -7248,31 +7248,31 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>-0.02217131000094649</v>
+        <v>-0.07156608984798039</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>1475</v>
+        <v>1582</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>業旺</t>
+          <t>信錦</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>91.907307958744</v>
+        <v>87.15083438819887</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>25.15</v>
+        <v>69.7</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -7283,13 +7283,13 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>37.63347121913982</v>
+        <v>44.55019263339418</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>12.97845718773578</v>
+        <v>13.61174415065277</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.8605540781852792</v>
+        <v>0.8072010357454377</v>
       </c>
       <c r="K129" s="2" t="n">
         <v>0</v>
@@ -7301,31 +7301,31 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>-0.04508345345407591</v>
+        <v>0.02941682395801343</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>1432</v>
+        <v>1324</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>大魯閣</t>
+          <t>地球</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>88.615759548664</v>
+        <v>81.0038828109212</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>14.95</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
@@ -7336,13 +7336,13 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>45.79822804316033</v>
+        <v>36.02925042354465</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>16.39808441898701</v>
+        <v>16.58413631569209</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>1.031039797491094</v>
+        <v>1.176250218738473</v>
       </c>
       <c r="K130" s="2" t="n">
         <v>0</v>
@@ -7354,31 +7354,31 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>-0.001578445013821088</v>
+        <v>-0.00972671555283941</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>1533</v>
+        <v>1227</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>車王電</t>
+          <t>佳格</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
         <v/>
       </c>
       <c r="D131" s="2" t="n">
-        <v>79.85901887365164</v>
+        <v>53.90453971069759</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>28.5</v>
+        <v>27.75</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -7389,13 +7389,13 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>33.26052361849224</v>
+        <v>43.40837100236789</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>13.54845663197638</v>
+        <v>17.77317528446641</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>0.4265565058770227</v>
+        <v>0.6902961814515265</v>
       </c>
       <c r="K131" s="2" t="n">
         <v>0</v>
@@ -7407,31 +7407,31 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>-0.05193207874577876</v>
+        <v>-0.02217130997291197</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>1417</v>
+        <v>1475</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>嘉裕</t>
+          <t>業旺</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
         <v/>
       </c>
       <c r="D132" s="2" t="n">
-        <v>78.82543723041415</v>
+        <v>31.90730795874419</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>8.09</v>
+        <v>25.15</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
@@ -7442,13 +7442,13 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>42.69079563475527</v>
+        <v>37.63347149330897</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>11.90022841243125</v>
+        <v>12.97845721820054</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>0.6149223717881894</v>
+        <v>0.8605540781852792</v>
       </c>
       <c r="K132" s="2" t="n">
         <v>0</v>
@@ -7460,31 +7460,31 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>0.001126261878761258</v>
+        <v>-0.04508345341202546</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>1471</v>
+        <v>1533</v>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>首利</t>
+          <t>車王電</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
         <v/>
       </c>
       <c r="D133" s="2" t="n">
-        <v>72.81128854837465</v>
+        <v>19.85901887365166</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>9.07</v>
+        <v>28.5</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -7495,13 +7495,13 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>39.95438539539683</v>
+        <v>33.26052271194548</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>14.71328547883567</v>
+        <v>13.54845658009269</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>0.7052728901524269</v>
+        <v>0.4265565058770227</v>
       </c>
       <c r="K133" s="2" t="n">
         <v>0</v>
@@ -7513,11 +7513,11 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>0.00395520683301645</v>
+        <v>-0.05193207814304979</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
